--- a/범운해운항공_전체데이터_통합백업_2026-10-28.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-28.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE84"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11132,6 +11132,671 @@
       </c>
       <c r="AE84" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BW-2026-090</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BW260039</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayra Armenta   </t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>21.5×19×9.5cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0.004 CBM</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>39840</v>
+      </c>
+      <c r="U85" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V85" t="n">
+        <v>4840</v>
+      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>1407 Magnolia Ave San Bernardino ca 92411</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>1-909-314-3403</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BW-2026-091</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BW260040</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daphne Ortiz  </t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>34.5×21×20cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0.014 CBM</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>119520</v>
+      </c>
+      <c r="U86" t="n">
+        <v>85000</v>
+      </c>
+      <c r="V86" t="n">
+        <v>34520</v>
+      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>154 State Street Penns Grove, NJ 08069, USA</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>1-856-275-1158</t>
+        </is>
+      </c>
+      <c r="AC86" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BW-2026-092</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BW260041</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alissa Fender </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>20.5×13×8cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0.002 CBM</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>39840</v>
+      </c>
+      <c r="U87" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4840</v>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>283 Brookstone Way, Jacksonville, NC, 28546, USA</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>1-910-381-9517</t>
+        </is>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BW-2026-093</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BW260042</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Quadrat Asuni</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>26×13×15cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0.005 CBM</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>79680</v>
+      </c>
+      <c r="U88" t="n">
+        <v>60000</v>
+      </c>
+      <c r="V88" t="n">
+        <v>19680</v>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>1955 Waters Branch Drive, Missouri City tx 77459</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>1-346-871-8692</t>
+        </is>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BW-2026-094</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BW260043</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Yordan Fernandez</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>33.5×26×20cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0.017 CBM</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>5</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>199200</v>
+      </c>
+      <c r="U89" t="n">
+        <v>135000</v>
+      </c>
+      <c r="V89" t="n">
+        <v>64200</v>
+      </c>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>3952 Cocoplum CIR #3643 E Karanda III Coconut Creek Florida USA, Zip 33063</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>1-786-961-5525</t>
+        </is>
+      </c>
+      <c r="AC89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-28.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-28.xlsx
@@ -11601,7 +11601,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>26×13×15cm(1CTN)</t>
+          <t>26×18.5×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
